--- a/data/outputs/extracted_rules.xlsx
+++ b/data/outputs/extracted_rules.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,6 +445,11 @@
       <c r="F1" t="inlineStr">
         <is>
           <t>page_no</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>station_id</t>
         </is>
       </c>
     </row>
@@ -499,6 +504,7 @@
       <c r="F2" t="n">
         <v>6</v>
       </c>
+      <c r="G2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -551,6 +557,7 @@
       <c r="F3" t="n">
         <v>6</v>
       </c>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -603,6 +610,7 @@
       <c r="F4" t="n">
         <v>6</v>
       </c>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -655,6 +663,7 @@
       <c r="F5" t="n">
         <v>6</v>
       </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -707,6 +716,7 @@
       <c r="F6" t="n">
         <v>6</v>
       </c>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -759,6 +769,7 @@
       <c r="F7" t="n">
         <v>6</v>
       </c>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -811,6 +822,7 @@
       <c r="F8" t="n">
         <v>6</v>
       </c>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -863,6 +875,525 @@
       <c r="F9" t="n">
         <v>6</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>station_reference</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 5 of 13
+3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
+any water.
+3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
+with manufacturer’s specifications.
+3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
+year for the purpose of this licence.
+3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
+(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
+than the Instream Objective of 0.16 cubic meters per second;
+(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
+greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
+per second;
+(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
+cubic meters per second; when the flow in the Blindman River is greater than 0.5
+cubic meters per second.
+3.15 The Licensee shall divert the water authorized by this licence only when there is
+sufficient flow in:
+(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
+(b) the Blindman River to meet or exceed the Instream Objective (IO)
+as specified in 3.16 and 3.17 respectively.
+3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
+Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>6</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>05CC002</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>station_reference</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 5 of 13
+3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
+any water.
+3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
+with manufacturer’s specifications.
+3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
+year for the purpose of this licence.
+3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
+(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
+than the Instream Objective of 0.16 cubic meters per second;
+(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
+greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
+per second;
+(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
+cubic meters per second; when the flow in the Blindman River is greater than 0.5
+cubic meters per second.
+3.15 The Licensee shall divert the water authorized by this licence only when there is
+sufficient flow in:
+(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
+(b) the Blindman River to meet or exceed the Instream Objective (IO)
+as specified in 3.16 and 3.17 respectively.
+3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
+Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>6</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>05CB007</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>station_reference</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 6 of 13
+3.19 Unless authorized in writing by the Director, the Blindman River Instream Objective is to
+be met:
+(a) at the Water Survey of Canada Station 05CC001 (Blindman River near Blackfalds)
+when it is operational; or
+(b) at the point of diversion when the WSC station 05CC001 is not operational;
+(c) when diverting any water.
+3.20 The Licensee shall not divert water when the water temperature in the source of water
+exceeds 22oC.
+MONITORING AND REPORTING
+4.0 Unless otherwise authorized in writing by the Director, the Licensee shall:
+(a) measure the total volume of water diverted each month, from the source of
+water, using the meter specified in 3.10(a);
+(b) measure the rate of diversion on a continuous basis, from the source of water,
+using the meter specified in 3.10(b);
+(c) measure or provide a Volume Estimate of the total volume of water used for each
+Associated Operation and the water use per well licenced under the Oil and Gas
+Conservation Act;
+(d) record the surface legal land location(s) where diverted water is being used, and
+the purpose/operation for which it is being used;
+(e) when applicable, measure the total volume of water released to the environment;
+(f) for the calendar year, compare the water diversion and usage as per 4.0 (a) to
+the estimates submitted with the Application and any previous reporting;
+(g) for the upcoming calendar year, prepare an overall estimate of the monthly water
+diversion and usage that i</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>station_reference</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 6 of 13
+3.19 Unless authorized in writing by the Director, the Blindman River Instream Objective is to
+be met:
+(a) at the Water Survey of Canada Station 05CC001 (Blindman River near Blackfalds)
+when it is operational; or
+(b) at the point of diversion when the WSC station 05CC001 is not operational;
+(c) when diverting any water.
+3.20 The Licensee shall not divert water when the water temperature in the source of water
+exceeds 22oC.
+MONITORING AND REPORTING
+4.0 Unless otherwise authorized in writing by the Director, the Licensee shall:
+(a) measure the total volume of water diverted each month, from the source of
+water, using the meter specified in 3.10(a);
+(b) measure the rate of diversion on a continuous basis, from the source of water,
+using the meter specified in 3.10(b);
+(c) measure or provide a Volume Estimate of the total volume of water used for each
+Associated Operation and the water use per well licenced under the Oil and Gas
+Conservation Act;
+(d) record the surface legal land location(s) where diverted water is being used, and
+the purpose/operation for which it is being used;
+(e) when applicable, measure the total volume of water released to the environment;
+(f) for the calendar year, compare the water diversion and usage as per 4.0 (a) to
+the estimates submitted with the Application and any previous reporting;
+(g) for the upcoming calendar year, prepare an overall estimate of the monthly water
+diversion and usage that i</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>station_reference</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 6 of 13
+3.19 Unless authorized in writing by the Director, the Blindman River Instream Objective is to
+be met:
+(a) at the Water Survey of Canada Station 05CC001 (Blindman River near Blackfalds)
+when it is operational; or
+(b) at the point of diversion when the WSC station 05CC001 is not operational;
+(c) when diverting any water.
+3.20 The Licensee shall not divert water when the water temperature in the source of water
+exceeds 22oC.
+MONITORING AND REPORTING
+4.0 Unless otherwise authorized in writing by the Director, the Licensee shall:
+(a) measure the total volume of water diverted each month, from the source of
+water, using the meter specified in 3.10(a);
+(b) measure the rate of diversion on a continuous basis, from the source of water,
+using the meter specified in 3.10(b);
+(c) measure or provide a Volume Estimate of the total volume of water used for each
+Associated Operation and the water use per well licenced under the Oil and Gas
+Conservation Act;
+(d) record the surface legal land location(s) where diverted water is being used, and
+the purpose/operation for which it is being used;
+(e) when applicable, measure the total volume of water released to the environment;
+(f) for the calendar year, compare the water diversion and usage as per 4.0 (a) to
+the estimates submitted with the Application and any previous reporting;
+(g) for the upcoming calendar year, prepare an overall estimate of the monthly water
+diversion and usage that i</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>station_reference</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence No.00458425-00-00
+File No.00458425
+Page 7 of 13
+(a) at the WSC Station No. 05CC001;
+(b) daily during diversion;
+or as otherwise authorized in writing by the Director.
+4.2 When the Water Survey of Canada Station No.05CC001 (Blindman River near
+Blackfalds) is not operational, the Licensee shall measure the rate of flow of water in the
+source:
+(a) at the point of diversion;
+(i) a minimum of weekly when the measured rate of flow is less than or equal to
+0.5 cubic metres per second;
+(ii) a minimum of bi-weekly when the measured rate of flow is greater than 0.5
+cubic meters per second.
+during diversion, or as otherwise authorized in writing by the Director.
+4.3 The Licensee shall monitor the rate of flow in the Red Deer River a minimum of bi-
+weekly during diversion.
+4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the
+source of water the point of diversion, at a minimum of the following:
+(a) prior to commencing diversion of water to establish a baseline temperature; and
+(b) if the baseline temperature:
+(i) is greater than 19oC, measure the temperature hourly during diversion; or
+(ii) any previous temperature measurement is less than 19oC, measure the
+temperature daily during diversion.
+4.5 The Licensee shall record and retain all of the following information for a minimum of 5
+years after being collected:
+(a) the place, date and time of all monitoring and measuring;
+(b) the results obtained pursuant to 4.0, 4.1, 4.2, 4.3 and 6.1; and
+(c) the </t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>8</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>station_reference</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence No.00458425-00-00
+File No.00458425
+Page 7 of 13
+(a) at the WSC Station No. 05CC001;
+(b) daily during diversion;
+or as otherwise authorized in writing by the Director.
+4.2 When the Water Survey of Canada Station No.05CC001 (Blindman River near
+Blackfalds) is not operational, the Licensee shall measure the rate of flow of water in the
+source:
+(a) at the point of diversion;
+(i) a minimum of weekly when the measured rate of flow is less than or equal to
+0.5 cubic metres per second;
+(ii) a minimum of bi-weekly when the measured rate of flow is greater than 0.5
+cubic meters per second.
+during diversion, or as otherwise authorized in writing by the Director.
+4.3 The Licensee shall monitor the rate of flow in the Red Deer River a minimum of bi-
+weekly during diversion.
+4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the
+source of water the point of diversion, at a minimum of the following:
+(a) prior to commencing diversion of water to establish a baseline temperature; and
+(b) if the baseline temperature:
+(i) is greater than 19oC, measure the temperature hourly during diversion; or
+(ii) any previous temperature measurement is less than 19oC, measure the
+temperature daily during diversion.
+4.5 The Licensee shall record and retain all of the following information for a minimum of 5
+years after being collected:
+(a) the place, date and time of all monitoring and measuring;
+(b) the results obtained pursuant to 4.0, 4.1, 4.2, 4.3 and 6.1; and
+(c) the </t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>8</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>station_reference</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 10 of 13
+SCHEDULE 1: Diversion Table
+Minimum
+Criteria Monitoring/Measuring
+Frequency
+When using When
+Flow in Blindman Maximum Rate of Diversion
+Station measuring
+River* (m3/s) (m3/s)
+05CC001 flows at POD
+0.16 ≥ Flow 0 (No Diversion allowed)
+Up to 10% of the flow, provided the
+diversion does not decrease the Weekly
+0.16 &lt; Flow ≤ 0.5
+Blindman River flow* to 0.16 m3/s Daily
+or lower
+15% of the flow up to a maximum
+Flow &gt; 0.5 14 days
+of 0.5 m3/s
+*Based on monitored flow at WSC Station 05CC001 (Blindman River at Blackfalds) when
+operational and measured flow at POD when WSC Station 05CC001 is not operational.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>11</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>station_reference</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 10 of 13
+SCHEDULE 1: Diversion Table
+Minimum
+Criteria Monitoring/Measuring
+Frequency
+When using When
+Flow in Blindman Maximum Rate of Diversion
+Station measuring
+River* (m3/s) (m3/s)
+05CC001 flows at POD
+0.16 ≥ Flow 0 (No Diversion allowed)
+Up to 10% of the flow, provided the
+diversion does not decrease the Weekly
+0.16 &lt; Flow ≤ 0.5
+Blindman River flow* to 0.16 m3/s Daily
+or lower
+15% of the flow up to a maximum
+Flow &gt; 0.5 14 days
+of 0.5 m3/s
+*Based on monitored flow at WSC Station 05CC001 (Blindman River at Blackfalds) when
+operational and measured flow at POD when WSC Station 05CC001 is not operational.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>11</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>station_reference</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 10 of 13
+SCHEDULE 1: Diversion Table
+Minimum
+Criteria Monitoring/Measuring
+Frequency
+When using When
+Flow in Blindman Maximum Rate of Diversion
+Station measuring
+River* (m3/s) (m3/s)
+05CC001 flows at POD
+0.16 ≥ Flow 0 (No Diversion allowed)
+Up to 10% of the flow, provided the
+diversion does not decrease the Weekly
+0.16 &lt; Flow ≤ 0.5
+Blindman River flow* to 0.16 m3/s Daily
+or lower
+15% of the flow up to a maximum
+Flow &gt; 0.5 14 days
+of 0.5 m3/s
+*Based on monitored flow at WSC Station 05CC001 (Blindman River at Blackfalds) when
+operational and measured flow at POD when WSC Station 05CC001 is not operational.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>11</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/outputs/extracted_rules.xlsx
+++ b/data/outputs/extracted_rules.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,15 +439,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>river</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>source_text</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>source_pdf</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>page_no</t>
         </is>
@@ -473,6 +478,11 @@
         </is>
       </c>
       <c r="E2" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -501,12 +511,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -530,6 +540,11 @@
         </is>
       </c>
       <c r="E3" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -558,12 +573,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -587,6 +602,11 @@
         </is>
       </c>
       <c r="E4" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -615,12 +635,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -644,6 +664,11 @@
         </is>
       </c>
       <c r="E5" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -672,12 +697,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -701,6 +726,11 @@
         </is>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -729,12 +759,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
         <v>6</v>
       </c>
     </row>
@@ -758,6 +788,11 @@
         </is>
       </c>
       <c r="E7" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -786,12 +821,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -815,6 +850,11 @@
         </is>
       </c>
       <c r="E8" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -843,12 +883,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>6</v>
       </c>
     </row>
@@ -872,6 +912,11 @@
         </is>
       </c>
       <c r="E9" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -900,12 +945,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
         <v>6</v>
       </c>
     </row>
@@ -929,6 +974,11 @@
         </is>
       </c>
       <c r="E10" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -957,12 +1007,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
         <v>6</v>
       </c>
     </row>
@@ -986,6 +1036,11 @@
         </is>
       </c>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -1014,12 +1069,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1043,6 +1098,11 @@
         </is>
       </c>
       <c r="E12" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -1071,12 +1131,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1100,6 +1160,11 @@
         </is>
       </c>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -1128,12 +1193,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1157,6 +1222,11 @@
         </is>
       </c>
       <c r="E14" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -1185,12 +1255,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1214,6 +1284,11 @@
         </is>
       </c>
       <c r="E15" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -1242,12 +1317,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1271,6 +1346,11 @@
         </is>
       </c>
       <c r="E16" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -1299,12 +1379,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1328,6 +1408,11 @@
         </is>
       </c>
       <c r="E17" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -1356,13 +1441,145 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>combined_rule</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence No.00458425-00-00
+File No.00458425
+Page 7 of 13
+(a) at the WSC Station No. 05CC001;
+(b) daily during diversion;
+or as otherwise authorized in writing by the Director.
+4.2 When the Water Survey of Canada Station No.05CC001 (Blindman River near
+Blackfalds) is not operational, the Licensee shall measure the rate of flow of water in the
+source:
+(a) at the point of diversion;
+(i) a minimum of weekly when the measured rate of flow is less than or equal to
+0.5 cubic metres per second;
+(ii) a minimum of bi-weekly when the measured rate of flow is greater than 0.5
+cubic meters per second.
+during diversion, or as otherwise authorized in writing by the Director.
+4.3 The Licensee shall monitor the rate of flow in the Red Deer River a minimum of bi-
+weekly during diversion.
+4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the
+source of water the point of diversion, at a minimum of the following:
+(a) prior to commencing diversion of water to establish a baseline temperature; and
+(b) if the baseline temperature:
+(i) is greater than 19oC, measure the temperature hourly during diversion; or
+(ii) any previous temperature measurement is less than 19oC, measure the
+temperature daily during diversion.
+4.5 The Licensee shall record and retain all of the following information for a minimum of 5
+years after being collected:
+(a) the place, date and time of all monitoring and measuring;
+(b) the results obtained pursuant to 4.0, 4.1, 4.2, 4.3 and 6.1; and
+(c) the </t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>combined_rule</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence No.00458425-00-00
+File No.00458425
+Page 7 of 13
+(a) at the WSC Station No. 05CC001;
+(b) daily during diversion;
+or as otherwise authorized in writing by the Director.
+4.2 When the Water Survey of Canada Station No.05CC001 (Blindman River near
+Blackfalds) is not operational, the Licensee shall measure the rate of flow of water in the
+source:
+(a) at the point of diversion;
+(i) a minimum of weekly when the measured rate of flow is less than or equal to
+0.5 cubic metres per second;
+(ii) a minimum of bi-weekly when the measured rate of flow is greater than 0.5
+cubic meters per second.
+during diversion, or as otherwise authorized in writing by the Director.
+4.3 The Licensee shall monitor the rate of flow in the Red Deer River a minimum of bi-
+weekly during diversion.
+4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the
+source of water the point of diversion, at a minimum of the following:
+(a) prior to commencing diversion of water to establish a baseline temperature; and
+(b) if the baseline temperature:
+(i) is greater than 19oC, measure the temperature hourly during diversion; or
+(ii) any previous temperature measurement is less than 19oC, measure the
+temperature daily during diversion.
+4.5 The Licensee shall record and retain all of the following information for a minimum of 5
+years after being collected:
+(a) the place, date and time of all monitoring and measuring;
+(b) the results obtained pursuant to 4.0, 4.1, 4.2, 4.3 and 6.1; and
+(c) the </t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/extracted_rules.xlsx
+++ b/data/outputs/extracted_rules.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,11 +471,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Red Deer River</t>
+          <t>Blindman River</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -484,12 +484,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>05CC002</t>
+          <t>05CC001</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Red Deer River at Red Deer</t>
+          <t>Blindman River near Blackfalds</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -538,11 +538,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Red Deer River</t>
+          <t>Blindman River</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>0.16</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -551,12 +551,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>05CB007</t>
+          <t>05CC001</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dickson Dam Tunnel Outlet</t>
+          <t>Blindman River near Blackfalds</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -597,6 +597,207 @@
         <v>6</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>combined_rule</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blindman River near Blackfalds</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 5 of 13
+3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
+any water.
+3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
+with manufacturer’s specifications.
+3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
+year for the purpose of this licence.
+3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
+(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
+than the Instream Objective of 0.16 cubic meters per second;
+(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
+greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
+per second;
+(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
+cubic meters per second; when the flow in the Blindman River is greater than 0.5
+cubic meters per second.
+3.15 The Licensee shall divert the water authorized by this licence only when there is
+sufficient flow in:
+(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
+(b) the Blindman River to meet or exceed the Instream Objective (IO)
+as specified in 3.16 and 3.17 respectively.
+3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
+Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>combined_rule</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Red Deer River</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>05CC002</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Red Deer River at Red Deer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 5 of 13
+3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
+any water.
+3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
+with manufacturer’s specifications.
+3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
+year for the purpose of this licence.
+3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
+(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
+than the Instream Objective of 0.16 cubic meters per second;
+(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
+greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
+per second;
+(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
+cubic meters per second; when the flow in the Blindman River is greater than 0.5
+cubic meters per second.
+3.15 The Licensee shall divert the water authorized by this licence only when there is
+sufficient flow in:
+(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
+(b) the Blindman River to meet or exceed the Instream Objective (IO)
+as specified in 3.16 and 3.17 respectively.
+3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
+Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>combined_rule</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Red Deer River</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>05CB007</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dickson Dam Tunnel Outlet</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 5 of 13
+3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
+any water.
+3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
+with manufacturer’s specifications.
+3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
+year for the purpose of this licence.
+3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
+(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
+than the Instream Objective of 0.16 cubic meters per second;
+(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
+greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
+per second;
+(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
+cubic meters per second; when the flow in the Blindman River is greater than 0.5
+cubic meters per second.
+3.15 The Licensee shall divert the water authorized by this licence only when there is
+sufficient flow in:
+(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
+(b) the Blindman River to meet or exceed the Instream Objective (IO)
+as specified in 3.16 and 3.17 respectively.
+3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
+Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/outputs/extracted_rules.xlsx
+++ b/data/outputs/extracted_rules.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,341 +461,6 @@
         <is>
           <t>page_no</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>combined_rule</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Blindman River</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>m3/s</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>05CC001</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Blindman River near Blackfalds</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Licence No.00458425-00-00
-File No.00458425
-Page 5 of 13
-3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
-any water.
-3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
-with manufacturer’s specifications.
-3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
-year for the purpose of this licence.
-3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
-(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
-than the Instream Objective of 0.16 cubic meters per second;
-(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
-greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
-per second;
-(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
-cubic meters per second; when the flow in the Blindman River is greater than 0.5
-cubic meters per second.
-3.15 The Licensee shall divert the water authorized by this licence only when there is
-sufficient flow in:
-(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
-(b) the Blindman River to meet or exceed the Instream Objective (IO)
-as specified in 3.16 and 3.17 respectively.
-3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
-Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>combined_rule</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Blindman River</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>m3/s</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>05CC001</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Blindman River near Blackfalds</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Licence No.00458425-00-00
-File No.00458425
-Page 5 of 13
-3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
-any water.
-3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
-with manufacturer’s specifications.
-3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
-year for the purpose of this licence.
-3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
-(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
-than the Instream Objective of 0.16 cubic meters per second;
-(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
-greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
-per second;
-(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
-cubic meters per second; when the flow in the Blindman River is greater than 0.5
-cubic meters per second.
-3.15 The Licensee shall divert the water authorized by this licence only when there is
-sufficient flow in:
-(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
-(b) the Blindman River to meet or exceed the Instream Objective (IO)
-as specified in 3.16 and 3.17 respectively.
-3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
-Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>combined_rule</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Blindman River</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>m3/s</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>05CC001</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Blindman River near Blackfalds</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Licence No.00458425-00-00
-File No.00458425
-Page 5 of 13
-3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
-any water.
-3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
-with manufacturer’s specifications.
-3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
-year for the purpose of this licence.
-3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
-(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
-than the Instream Objective of 0.16 cubic meters per second;
-(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
-greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
-per second;
-(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
-cubic meters per second; when the flow in the Blindman River is greater than 0.5
-cubic meters per second.
-3.15 The Licensee shall divert the water authorized by this licence only when there is
-sufficient flow in:
-(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
-(b) the Blindman River to meet or exceed the Instream Objective (IO)
-as specified in 3.16 and 3.17 respectively.
-3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
-Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>combined_rule</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Red Deer River</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>16</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>m3/s</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>05CC002</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Red Deer River at Red Deer</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Licence No.00458425-00-00
-File No.00458425
-Page 5 of 13
-3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
-any water.
-3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
-with manufacturer’s specifications.
-3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
-year for the purpose of this licence.
-3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
-(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
-than the Instream Objective of 0.16 cubic meters per second;
-(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
-greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
-per second;
-(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
-cubic meters per second; when the flow in the Blindman River is greater than 0.5
-cubic meters per second.
-3.15 The Licensee shall divert the water authorized by this licence only when there is
-sufficient flow in:
-(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
-(b) the Blindman River to meet or exceed the Instream Objective (IO)
-as specified in 3.16 and 3.17 respectively.
-3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
-Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>combined_rule</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Red Deer River</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>16</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>m3/s</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>05CB007</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Dickson Dam Tunnel Outlet</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Licence No.00458425-00-00
-File No.00458425
-Page 5 of 13
-3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
-any water.
-3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
-with manufacturer’s specifications.
-3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
-year for the purpose of this licence.
-3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
-(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
-than the Instream Objective of 0.16 cubic meters per second;
-(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
-greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
-per second;
-(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
-cubic meters per second; when the flow in the Blindman River is greater than 0.5
-cubic meters per second.
-3.15 The Licensee shall divert the water authorized by this licence only when there is
-sufficient flow in:
-(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
-(b) the Blindman River to meet or exceed the Instream Objective (IO)
-as specified in 3.16 and 3.17 respectively.
-3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
-Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/extracted_rules.xlsx
+++ b/data/outputs/extracted_rules.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,6 +461,341 @@
         <is>
           <t>page_no</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>combined_rule</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Blindman River near Blackfalds</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 5 of 13
+3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
+any water.
+3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
+with manufacturer’s specifications.
+3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
+year for the purpose of this licence.
+3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
+(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
+than the Instream Objective of 0.16 cubic meters per second;
+(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
+greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
+per second;
+(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
+cubic meters per second; when the flow in the Blindman River is greater than 0.5
+cubic meters per second.
+3.15 The Licensee shall divert the water authorized by this licence only when there is
+sufficient flow in:
+(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
+(b) the Blindman River to meet or exceed the Instream Objective (IO)
+as specified in 3.16 and 3.17 respectively.
+3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
+Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>combined_rule</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blindman River near Blackfalds</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 5 of 13
+3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
+any water.
+3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
+with manufacturer’s specifications.
+3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
+year for the purpose of this licence.
+3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
+(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
+than the Instream Objective of 0.16 cubic meters per second;
+(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
+greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
+per second;
+(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
+cubic meters per second; when the flow in the Blindman River is greater than 0.5
+cubic meters per second.
+3.15 The Licensee shall divert the water authorized by this licence only when there is
+sufficient flow in:
+(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
+(b) the Blindman River to meet or exceed the Instream Objective (IO)
+as specified in 3.16 and 3.17 respectively.
+3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
+Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>combined_rule</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blindman River near Blackfalds</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 5 of 13
+3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
+any water.
+3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
+with manufacturer’s specifications.
+3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
+year for the purpose of this licence.
+3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
+(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
+than the Instream Objective of 0.16 cubic meters per second;
+(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
+greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
+per second;
+(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
+cubic meters per second; when the flow in the Blindman River is greater than 0.5
+cubic meters per second.
+3.15 The Licensee shall divert the water authorized by this licence only when there is
+sufficient flow in:
+(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
+(b) the Blindman River to meet or exceed the Instream Objective (IO)
+as specified in 3.16 and 3.17 respectively.
+3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
+Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>combined_rule</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Red Deer River</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>16</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>05CC002</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Red Deer River at Red Deer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 5 of 13
+3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
+any water.
+3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
+with manufacturer’s specifications.
+3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
+year for the purpose of this licence.
+3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
+(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
+than the Instream Objective of 0.16 cubic meters per second;
+(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
+greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
+per second;
+(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
+cubic meters per second; when the flow in the Blindman River is greater than 0.5
+cubic meters per second.
+3.15 The Licensee shall divert the water authorized by this licence only when there is
+sufficient flow in:
+(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
+(b) the Blindman River to meet or exceed the Instream Objective (IO)
+as specified in 3.16 and 3.17 respectively.
+3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
+Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>combined_rule</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Red Deer River</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>05CB007</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dickson Dam Tunnel Outlet</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 5 of 13
+3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
+any water.
+3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
+with manufacturer’s specifications.
+3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
+year for the purpose of this licence.
+3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
+(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
+than the Instream Objective of 0.16 cubic meters per second;
+(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
+greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
+per second;
+(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
+cubic meters per second; when the flow in the Blindman River is greater than 0.5
+cubic meters per second.
+3.15 The Licensee shall divert the water authorized by this licence only when there is
+sufficient flow in:
+(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
+(b) the Blindman River to meet or exceed the Instream Objective (IO)
+as specified in 3.16 and 3.17 respectively.
+3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
+Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/extracted_rules.xlsx
+++ b/data/outputs/extracted_rules.xlsx
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>combined_rule</t>
+          <t>no_diversion</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>combined_rule</t>
+          <t>instream_objective</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -600,7 +600,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>combined_rule</t>
+          <t>flow_threshold</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -667,7 +667,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>combined_rule</t>
+          <t>water_conservation_objective</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -734,7 +734,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>combined_rule</t>
+          <t>water_conservation_objective</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">

--- a/data/outputs/extracted_rules.xlsx
+++ b/data/outputs/extracted_rules.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,30 +434,35 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>units</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>station_id</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>station_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>source_text</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>source_pdf</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>page_no</t>
         </is>
@@ -477,22 +482,23 @@
       <c r="C2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -521,12 +527,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -544,22 +550,23 @@
       <c r="C3" t="n">
         <v>0.16</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -588,12 +595,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -611,22 +618,23 @@
       <c r="C4" t="n">
         <v>0.5</v>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -655,12 +663,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -678,22 +686,23 @@
       <c r="C5" t="n">
         <v>16</v>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>05CC002</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Red Deer River at Red Deer</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -722,12 +731,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -745,22 +754,23 @@
       <c r="C6" t="n">
         <v>16</v>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>05CB007</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Dickson Dam Tunnel Outlet</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -789,12 +799,140 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>percent_diversion</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>10</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Blindman River near Blackfalds</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 5 of 13
+3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
+any water.
+3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
+with manufacturer’s specifications.
+3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
+year for the purpose of this licence.
+3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
+(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
+than the Instream Objective of 0.16 cubic meters per second;
+(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
+greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
+per second;
+(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
+cubic meters per second; when the flow in the Blindman River is greater than 0.5
+cubic meters per second.
+3.15 The Licensee shall divert the water authorized by this licence only when there is
+sufficient flow in:
+(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
+(b) the Blindman River to meet or exceed the Instream Objective (IO)
+as specified in 3.16 and 3.17 respectively.
+3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
+Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>percent_diversion</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Blindman River</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Blindman River near Blackfalds</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 5 of 13
+3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
+any water.
+3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
+with manufacturer’s specifications.
+3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
+year for the purpose of this licence.
+3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
+(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
+than the Instream Objective of 0.16 cubic meters per second;
+(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
+greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
+per second;
+(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
+cubic meters per second; when the flow in the Blindman River is greater than 0.5
+cubic meters per second.
+3.15 The Licensee shall divert the water authorized by this licence only when there is
+sufficient flow in:
+(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
+(b) the Blindman River to meet or exceed the Instream Objective (IO)
+as specified in 3.16 and 3.17 respectively.
+3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
+Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
         <v>6</v>
       </c>
     </row>

--- a/data/outputs/extracted_rules.xlsx
+++ b/data/outputs/extracted_rules.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Blindman River</t>
+          <t>Blindman</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -544,7 +544,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Blindman River</t>
+          <t>Blindman</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blindman River</t>
+          <t>Blindman</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -680,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Red Deer River</t>
+          <t>Red Deer</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -748,7 +748,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Red Deer River</t>
+          <t>Red Deer</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -816,7 +816,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Blindman River</t>
+          <t>Blindman</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -880,7 +880,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Blindman River</t>
+          <t>Blindman</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>

--- a/data/outputs/extracted_rules.xlsx
+++ b/data/outputs/extracted_rules.xlsx
@@ -471,7 +471,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>no_diversion</t>
+          <t>instream_objective</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -500,31 +500,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Licence No.00458425-00-00
-File No.00458425
-Page 5 of 13
-3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
-any water.
-3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
-with manufacturer’s specifications.
-3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
-year for the purpose of this licence.
-3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
-(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
-than the Instream Objective of 0.16 cubic meters per second;
-(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
-greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
-per second;
-(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
-cubic meters per second; when the flow in the Blindman River is greater than 0.5
-cubic meters per second.
-3.15 The Licensee shall divert the water authorized by this licence only when there is
-sufficient flow in:
-(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
-(b) the Blindman River to meet or exceed the Instream Objective (IO)
-as specified in 3.16 and 3.17 respectively.
-3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
-Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+          <t>(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less than the Instream Objective of 0.16 cubic meters per second;</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -568,31 +544,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Licence No.00458425-00-00
-File No.00458425
-Page 5 of 13
-3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
-any water.
-3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
-with manufacturer’s specifications.
-3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
-year for the purpose of this licence.
-3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
-(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
-than the Instream Objective of 0.16 cubic meters per second;
-(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
-greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
-per second;
-(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
-cubic meters per second; when the flow in the Blindman River is greater than 0.5
-cubic meters per second.
-3.15 The Licensee shall divert the water authorized by this licence only when there is
-sufficient flow in:
-(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
-(b) the Blindman River to meet or exceed the Instream Objective (IO)
-as specified in 3.16 and 3.17 respectively.
-3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
-Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+          <t>(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less than the Instream Objective of 0.16 cubic meters per second;</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -607,16 +559,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>flow_threshold</t>
+          <t>water_conservation_objective</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blindman</t>
+          <t>Red Deer</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5</v>
+        <v>16</v>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
@@ -626,41 +578,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>05CC001</t>
+          <t>05CC002</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Blindman River near Blackfalds</t>
+          <t>Red Deer River at Red Deer</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Licence No.00458425-00-00
-File No.00458425
-Page 5 of 13
-3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
-any water.
-3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
-with manufacturer’s specifications.
-3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
-year for the purpose of this licence.
-3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
-(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
-than the Instream Objective of 0.16 cubic meters per second;
-(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
-greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
-per second;
-(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
-cubic meters per second; when the flow in the Blindman River is greater than 0.5
-cubic meters per second.
-3.15 The Licensee shall divert the water authorized by this licence only when there is
-sufficient flow in:
-(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
-(b) the Blindman River to meet or exceed the Instream Objective (IO)
-as specified in 3.16 and 3.17 respectively.
-3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
-Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+          <t>3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red Deer River that is 45% of the natural rate of flow or 16 cubic meters per second, whichever is greater at any point in time.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -694,41 +622,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>05CC002</t>
+          <t>05CB007</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Red Deer River at Red Deer</t>
+          <t>Dickson Dam Tunnel Outlet</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Licence No.00458425-00-00
-File No.00458425
-Page 5 of 13
-3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
-any water.
-3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
-with manufacturer’s specifications.
-3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
-year for the purpose of this licence.
-3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
-(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
-than the Instream Objective of 0.16 cubic meters per second;
-(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
-greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
-per second;
-(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
-cubic meters per second; when the flow in the Blindman River is greater than 0.5
-cubic meters per second.
-3.15 The Licensee shall divert the water authorized by this licence only when there is
-sufficient flow in:
-(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
-(b) the Blindman River to meet or exceed the Instream Objective (IO)
-as specified in 3.16 and 3.17 respectively.
-3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
-Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+          <t>3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red Deer River that is 45% of the natural rate of flow or 16 cubic meters per second, whichever is greater at any point in time.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -743,16 +647,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>water_conservation_objective</t>
+          <t>instream_objective</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Red Deer</t>
+          <t>Blindman</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>0.16</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
@@ -762,41 +666,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>05CB007</t>
+          <t>05CC001</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dickson Dam Tunnel Outlet</t>
+          <t>Blindman River near Blackfalds</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Licence No.00458425-00-00
-File No.00458425
-Page 5 of 13
-3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
-any water.
-3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
-with manufacturer’s specifications.
-3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
-year for the purpose of this licence.
-3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
-(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
-than the Instream Objective of 0.16 cubic meters per second;
-(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
-greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
-per second;
-(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
-cubic meters per second; when the flow in the Blindman River is greater than 0.5
-cubic meters per second.
-3.15 The Licensee shall divert the water authorized by this licence only when there is
-sufficient flow in:
-(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
-(b) the Blindman River to meet or exceed the Instream Objective (IO)
-as specified in 3.16 and 3.17 respectively.
-3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
-Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+          <t>3.17 The Instream Objective for the Blindman River is a rate of flow in the Blindman River of 0.16 cubic meters per second.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -836,31 +716,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Licence No.00458425-00-00
-File No.00458425
-Page 5 of 13
-3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
-any water.
-3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
-with manufacturer’s specifications.
-3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
-year for the purpose of this licence.
-3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
-(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
-than the Instream Objective of 0.16 cubic meters per second;
-(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
-greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
-per second;
-(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
-cubic meters per second; when the flow in the Blindman River is greater than 0.5
-cubic meters per second.
-3.15 The Licensee shall divert the water authorized by this licence only when there is
-sufficient flow in:
-(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
-(b) the Blindman River to meet or exceed the Instream Objective (IO)
-as specified in 3.16 and 3.17 respectively.
-3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
-Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+          <t>(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters per second;</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -900,31 +756,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Licence No.00458425-00-00
-File No.00458425
-Page 5 of 13
-3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
-any water.
-3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
-with manufacturer’s specifications.
-3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
-year for the purpose of this licence.
-3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
-(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
-than the Instream Objective of 0.16 cubic meters per second;
-(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
-greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
-per second;
-(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
-cubic meters per second; when the flow in the Blindman River is greater than 0.5
-cubic meters per second.
-3.15 The Licensee shall divert the water authorized by this licence only when there is
-sufficient flow in:
-(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
-(b) the Blindman River to meet or exceed the Instream Objective (IO)
-as specified in 3.16 and 3.17 respectively.
-3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
-Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
+          <t>(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5 cubic meters per second; when the flow in the Blindman River is greater than 0.5 cubic meters per second.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">

--- a/data/outputs/extracted_rules.xlsx
+++ b/data/outputs/extracted_rules.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,45 +424,75 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>condition_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>season_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>start_month</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>start_day</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>end_month</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>end_day</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>river</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>threshold_value</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>units</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>station_id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>station_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>source_text</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>source_pdf</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>page_no</t>
         </is>
@@ -474,41 +504,47 @@
           <t>instream_objective</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
         <is>
           <t>Blindman</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="I2" t="n">
         <v>0</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less than the Instream Objective of 0.16 cubic meters per second;</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -518,41 +554,47 @@
           <t>instream_objective</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
         <is>
           <t>Blindman</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="I3" t="n">
         <v>0.16</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less than the Instream Objective of 0.16 cubic meters per second;</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="J3" t="n">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -562,41 +604,47 @@
           <t>water_conservation_objective</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Red Deer</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="I4" t="n">
         <v>16</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>05CC002</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Red Deer River at Red Deer</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red Deer River that is 45% of the natural rate of flow or 16 cubic meters per second, whichever is greater at any point in time.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -606,41 +654,47 @@
           <t>water_conservation_objective</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
         <is>
           <t>Red Deer</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="I5" t="n">
         <v>16</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>05CB007</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Dickson Dam Tunnel Outlet</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red Deer River that is 45% of the natural rate of flow or 16 cubic meters per second, whichever is greater at any point in time.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="J5" t="n">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -650,41 +704,47 @@
           <t>instream_objective</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
         <is>
           <t>Blindman</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="I6" t="n">
         <v>0.16</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>3.17 The Instream Objective for the Blindman River is a rate of flow in the Blindman River of 0.16 cubic meters per second.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="J6" t="n">
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
         <v>6</v>
       </c>
     </row>
@@ -694,37 +754,43 @@
           <t>percent_diversion</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
         <is>
           <t>Blindman</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="n">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
         <v>10</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters per second;</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -734,38 +800,476 @@
           <t>percent_diversion</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
         <is>
           <t>Blindman</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="n">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
         <v>15</v>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5 cubic meters per second; when the flow in the Blindman River is greater than 0.5 cubic meters per second.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>seasonal_window</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>seasonal_condition_unknown</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>winter</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Red Deer</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>05CC002</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Red Deer River at Red Deer</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>during the open water season; or (b) at the Water Survey of Canada Station 05CB007 (Dickson Dam Tunnel Outlet) during the winter ice cover season;</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>seasonal_window</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>seasonal_condition_unknown</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>winter</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Red Deer</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>05CB007</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Dickson Dam Tunnel Outlet</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>during the open water season; or (b) at the Water Survey of Canada Station 05CB007 (Dickson Dam Tunnel Outlet) during the winter ice cover season;</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>seasonal_window</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>seasonal_condition_unknown</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>open_water_season</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Red Deer</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>05CC002</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Red Deer River at Red Deer</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>during the open water season; or (b) at the Water Survey of Canada Station 05CB007 (Dickson Dam Tunnel Outlet) during the winter ice cover season;</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>seasonal_window</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>seasonal_condition_unknown</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>open_water_season</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Red Deer</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>05CB007</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Dickson Dam Tunnel Outlet</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>during the open water season; or (b) at the Water Survey of Canada Station 05CB007 (Dickson Dam Tunnel Outlet) during the winter ice cover season;</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>seasonal_window</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>seasonal_condition_unknown</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>date_range</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Red Deer</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>05CC002</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Red Deer River at Red Deer</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the source of water the point of diversion, at a minimum of the following:</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>seasonal_window</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>seasonal_condition_unknown</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>date_range</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Red Deer</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>05CB007</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Dickson Dam Tunnel Outlet</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the source of water the point of diversion, at a minimum of the following:</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>seasonal_condition_text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>seasonal_condition_unknown</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Red Deer</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>05CC002</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Red Deer River at Red Deer</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the source of water the point of diversion, at a minimum of the following:</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>seasonal_condition_text</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>seasonal_condition_unknown</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Red Deer</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>05CB007</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Dickson Dam Tunnel Outlet</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the source of water the point of diversion, at a minimum of the following:</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/extracted_rules.xlsx
+++ b/data/outputs/extracted_rules.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>water_conservation_objective</t>
+          <t>instream_objective</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -512,11 +512,11 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Red Deer</t>
+          <t>Blindman</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
@@ -526,17 +526,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>05CC002</t>
+          <t>05CC001</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Red Deer River at Red Deer</t>
+          <t>Blindman River near Blackfalds</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red Deer River that is 45% of the natural rate of flow or 16 cubic meters per second, whichever is greater at any point in time.</t>
+          <t>(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less than the Instream Objective of 0.16 cubic meters per second;</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -551,7 +551,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>water_conservation_objective</t>
+          <t>instream_objective</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -562,11 +562,11 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Red Deer</t>
+          <t>Blindman</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>0.16</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
@@ -576,17 +576,17 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>05CB007</t>
+          <t>05CC001</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Dickson Dam Tunnel Outlet</t>
+          <t>Blindman River near Blackfalds</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red Deer River that is 45% of the natural rate of flow or 16 cubic meters per second, whichever is greater at any point in time.</t>
+          <t>(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less than the Instream Objective of 0.16 cubic meters per second;</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -601,19 +601,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>seasonal_window</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>seasonal_condition_unknown</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>winter</t>
-        </is>
-      </c>
+          <t>water_conservation_objective</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
@@ -623,22 +615,28 @@
           <t>Red Deer</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="n">
+        <v>16</v>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>05CB007</t>
+          <t>05CC002</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Dickson Dam Tunnel Outlet</t>
+          <t>Red Deer River at Red Deer</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>during the open water season; or (b) at the Water Survey of Canada Station 05CB007 (Dickson Dam Tunnel Outlet) during the winter ice cover season;</t>
+          <t>3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red Deer River that is 45% of the natural rate of flow or 16 cubic meters per second, whichever is greater at any point in time.</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -648,6 +646,378 @@
       </c>
       <c r="P4" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>water_conservation_objective</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Red Deer</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>16</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>05CB007</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Dickson Dam Tunnel Outlet</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red Deer River that is 45% of the natural rate of flow or 16 cubic meters per second, whichever is greater at any point in time.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>instream_objective</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Blindman</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Blindman River near Blackfalds</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>3.17 The Instream Objective for the Blindman River is a rate of flow in the Blindman River of 0.16 cubic meters per second.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>percent_diversion</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Blindman</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Blindman River near Blackfalds</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters per second;</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>percent_diversion</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Blindman</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>15</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Blindman River near Blackfalds</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5 cubic meters per second; when the flow in the Blindman River is greater than 0.5 cubic meters per second.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>seasonal_window</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>seasonal_condition_unknown</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>winter</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Red Deer</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>05CB007</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Dickson Dam Tunnel Outlet</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>during the open water season; or (b) at the Water Survey of Canada Station 05CB007 (Dickson Dam Tunnel Outlet) during the winter ice cover season;</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>seasonal_window</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>seasonal_condition_unknown</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>date_range</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Red Deer</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>05CC002</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Red Deer River at Red Deer</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the source of water the point of diversion, at a minimum of the following:</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>seasonal_window</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>seasonal_condition_unknown</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>date_range</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Red Deer</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>05CB007</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Dickson Dam Tunnel Outlet</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the source of water the point of diversion, at a minimum of the following:</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/extracted_rules.xlsx
+++ b/data/outputs/extracted_rules.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:S13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,65 +434,80 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>temperature_rule_type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>start_month</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>start_day</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>end_month</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>end_day</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>river</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>threshold_value</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>temperature_c</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>frequency</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>units</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>station_id</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>station_name</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>source_text</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>source_pdf</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>page_no</t>
         </is>
@@ -510,41 +525,44 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Blindman</t>
         </is>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less than the Instream Objective of 0.16 cubic meters per second;</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -560,41 +578,44 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Blindman</t>
         </is>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>0.16</v>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less than the Instream Objective of 0.16 cubic meters per second;</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -610,41 +631,44 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>Red Deer</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>16</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>05CC002</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>Red Deer River at Red Deer</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red Deer River that is 45% of the natural rate of flow or 16 cubic meters per second, whichever is greater at any point in time.</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -660,48 +684,51 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>Red Deer</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>16</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>05CB007</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Dickson Dam Tunnel Outlet</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red Deer River that is 45% of the natural rate of flow or 16 cubic meters per second, whichever is greater at any point in time.</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="P5" t="n">
+      <c r="S5" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>instream_objective</t>
+          <t>percent_diversion</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -710,41 +737,40 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>Blindman</t>
         </is>
       </c>
-      <c r="I6" t="n">
-        <v>0.16</v>
-      </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>m3/s</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="n">
+        <v>10</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>3.17 The Instream Objective for the Blindman River is a rate of flow in the Blindman River of 0.16 cubic meters per second.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters per second;</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
         <v>6</v>
       </c>
     </row>
@@ -760,264 +786,387 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Blindman</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>10</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="L7" t="n">
+        <v>15</v>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters per second;</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5 cubic meters per second; when the flow in the Blindman River is greater than 0.5 cubic meters per second.</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="P7" t="n">
+      <c r="S7" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>percent_diversion</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+          <t>seasonal_window</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>seasonal_condition_unknown</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>open_water_season</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Blindman</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>15</v>
-      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Red Deer</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>05CC001</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Blindman River near Blackfalds</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5 cubic meters per second; when the flow in the Blindman River is greater than 0.5 cubic meters per second.</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
+          <t>05CB007</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Dickson Dam Tunnel Outlet</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>during the open water season; or (b) at the Water Survey of Canada Station 05CB007 (Dickson Dam Tunnel Outlet) during the winter ice cover season;</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>seasonal_window</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>seasonal_condition_unknown</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>winter</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>temperature_rule</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>temperature_monitoring_frequency</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Red Deer</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Blindman</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>05CB007</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Dickson Dam Tunnel Outlet</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>during the open water season; or (b) at the Water Survey of Canada Station 05CB007 (Dickson Dam Tunnel Outlet) during the winter ice cover season;</t>
-        </is>
-      </c>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Blindman River near Blackfalds</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>(b) daily during diversion;</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="P9" t="n">
-        <v>6</v>
+      <c r="S9" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>seasonal_window</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>seasonal_condition_unknown</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>date_range</t>
-        </is>
-      </c>
+          <t>temperature_window</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
+          <t>monitoring_period</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>June</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>1</v>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>1</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Red Deer</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
         <is>
           <t>05CC002</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>Red Deer River at Red Deer</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the source of water the point of diversion, at a minimum of the following:</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="P10" t="n">
+      <c r="S10" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>seasonal_window</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>seasonal_condition_unknown</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>date_range</t>
-        </is>
-      </c>
+          <t>temperature_window</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
+          <t>monitoring_period</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>June</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>1</v>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>1</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Red Deer</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
         <is>
           <t>05CB007</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Dickson Dam Tunnel Outlet</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the source of water the point of diversion, at a minimum of the following:</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>temperature_rule</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>temperature_monitoring_frequency</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Blindman</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Blindman River near Blackfalds</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00 File No.00458425 Page 10 of 13 SCHEDULE 1: Diversion Table Minimum Criteria Monitoring/Measuring Frequency When using When Flow in Blindman Maximum Rate of Diversion Station measuring River* (m3/s) (m3/s) 05CC001 flows at POD 0.16 ≥ Flow 0 (No Diversion allowed) Up to 10% of the flow, provided the diversion does not decrease the Weekly 0.16 &lt; Flow ≤ 0.5 Blindman River flow* to 0.16 m3/s Daily or lower 15% of the flow up to a maximum Flow &gt; 0.5 14 days of 0.5 m3/s *Based on monitored flow at WSC Station 05CC001 (Blindman River at Blackfalds) when</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>temperature_rule</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>temperature_monitoring_frequency</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Blindman</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>05CC001</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Blindman River near Blackfalds</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Licence No.00458425-00-00 File No.00458425 Page 10 of 13 SCHEDULE 1: Diversion Table Minimum Criteria Monitoring/Measuring Frequency When using When Flow in Blindman Maximum Rate of Diversion Station measuring River* (m3/s) (m3/s) 05CC001 flows at POD 0.16 ≥ Flow 0 (No Diversion allowed) Up to 10% of the flow, provided the diversion does not decrease the Weekly 0.16 &lt; Flow ≤ 0.5 Blindman River flow* to 0.16 m3/s Daily or lower 15% of the flow up to a maximum Flow &gt; 0.5 14 days of 0.5 m3/s *Based on monitored flow at WSC Station 05CC001 (Blindman River at Blackfalds) when</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/extracted_rules.xlsx
+++ b/data/outputs/extracted_rules.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -831,12 +831,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>seasonal_condition_unknown</t>
+          <t>seasonal_station_applicability</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>open_water_season</t>
+          <t>winter_ice_cover_season</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -881,47 +881,55 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>temperature_rule</t>
+          <t>temperature_window</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>temperature_monitoring_frequency</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+          <t>monitoring_period</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Blindman</t>
+          <t>Red Deer</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>05CC001</t>
+          <t>05CC002</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Blindman River near Blackfalds</t>
+          <t>Red Deer River at Red Deer</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>(b) daily during diversion;</t>
+          <t>4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the source of water the point of diversion, at a minimum of the following:</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -974,12 +982,12 @@
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>05CC002</t>
+          <t>05CB007</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Red Deer River at Red Deer</t>
+          <t>Dickson Dam Tunnel Outlet</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -994,179 +1002,6 @@
       </c>
       <c r="S10" t="n">
         <v>8</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>temperature_window</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>monitoring_period</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>June</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>October</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Red Deer</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>05CB007</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Dickson Dam Tunnel Outlet</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the source of water the point of diversion, at a minimum of the following:</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>temperature_rule</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>temperature_monitoring_frequency</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Blindman</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>05CC001</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Blindman River near Blackfalds</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Licence No.00458425-00-00 File No.00458425 Page 10 of 13 SCHEDULE 1: Diversion Table Minimum Criteria Monitoring/Measuring Frequency When using When Flow in Blindman Maximum Rate of Diversion Station measuring River* (m3/s) (m3/s) 05CC001 flows at POD 0.16 ≥ Flow 0 (No Diversion allowed) Up to 10% of the flow, provided the diversion does not decrease the Weekly 0.16 &lt; Flow ≤ 0.5 Blindman River flow* to 0.16 m3/s Daily or lower 15% of the flow up to a maximum Flow &gt; 0.5 14 days of 0.5 m3/s *Based on monitored flow at WSC Station 05CC001 (Blindman River at Blackfalds) when</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="S12" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>temperature_rule</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>temperature_monitoring_frequency</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Blindman</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>05CC001</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Blindman River near Blackfalds</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Licence No.00458425-00-00 File No.00458425 Page 10 of 13 SCHEDULE 1: Diversion Table Minimum Criteria Monitoring/Measuring Frequency When using When Flow in Blindman Maximum Rate of Diversion Station measuring River* (m3/s) (m3/s) 05CC001 flows at POD 0.16 ≥ Flow 0 (No Diversion allowed) Up to 10% of the flow, provided the diversion does not decrease the Weekly 0.16 &lt; Flow ≤ 0.5 Blindman River flow* to 0.16 m3/s Daily or lower 15% of the flow up to a maximum Flow &gt; 0.5 14 days of 0.5 m3/s *Based on monitored flow at WSC Station 05CC001 (Blindman River at Blackfalds) when</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>00458425-00-00.pdf</t>
-        </is>
-      </c>
-      <c r="S13" t="n">
-        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/data/outputs/extracted_rules.xlsx
+++ b/data/outputs/extracted_rules.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -836,7 +836,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>winter_ice_cover_season</t>
+          <t>open_water_season</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -856,17 +856,41 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>05CB007</t>
+          <t>05CC002</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dickson Dam Tunnel Outlet</t>
+          <t>Red Deer River at Red Deer</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>during the open water season; or (b) at the Water Survey of Canada Station 05CB007 (Dickson Dam Tunnel Outlet) during the winter ice cover season;</t>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 5 of 13
+3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
+any water.
+3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
+with manufacturer’s specifications.
+3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
+year for the purpose of this licence.
+3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
+(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
+than the Instream Objective of 0.16 cubic meters per second;
+(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
+greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
+per second;
+(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
+cubic meters per second; when the flow in the Blindman River is greater than 0.5
+cubic meters per second.
+3.15 The Licensee shall divert the water authorized by this licence only when there is
+sufficient flow in:
+(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
+(b) the Blindman River to meet or exceed the Instream Objective (IO)
+as specified in 3.16 and 3.17 respectively.
+3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
+Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -881,32 +905,24 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>temperature_window</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>monitoring_period</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>June</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>October</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
+          <t>seasonal_window</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>seasonal_station_applicability</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>winter_ice_cover_season</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Red Deer</t>
@@ -919,17 +935,41 @@
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>05CC002</t>
+          <t>05CB007</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Red Deer River at Red Deer</t>
+          <t>Dickson Dam Tunnel Outlet</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the source of water the point of diversion, at a minimum of the following:</t>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 5 of 13
+3.11 The Licensee shall maintain each measuring device referred to in 3.10 when diverting
+any water.
+3.12 The Licensee shall calibrate each measuring device referred to in 3.10 in accordance
+with manufacturer’s specifications.
+3.13 The Licensee shall not divert more than 1,000,000 cubic metres of water per calendar
+year for the purpose of this licence.
+3.14 The Licensee shall not divert from the source of water at a rate of diversion greater than:
+(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less
+than the Instream Objective of 0.16 cubic meters per second;
+(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is
+greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters
+per second;
+(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5
+cubic meters per second; when the flow in the Blindman River is greater than 0.5
+cubic meters per second.
+3.15 The Licensee shall divert the water authorized by this licence only when there is
+sufficient flow in:
+(a) the Red Deer River to meet or exceed the Water Conservation Objective; and
+(b) the Blindman River to meet or exceed the Instream Objective (IO)
+as specified in 3.16 and 3.17 respectively.
+3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red
+Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -938,61 +978,73 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>temperature_window</t>
+          <t>temperature_rule</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>monitoring_period</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>June</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>October</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
+          <t>temperature_maximum</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Red Deer</t>
+          <t>Blindman</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="n">
+        <v>22</v>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>05CB007</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Dickson Dam Tunnel Outlet</t>
-        </is>
-      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the source of water the point of diversion, at a minimum of the following:</t>
+          <t>Licence No.00458425-00-00
+File No.00458425
+Page 6 of 13
+3.19 Unless authorized in writing by the Director, the Blindman River Instream Objective is to
+be met:
+(a) at the Water Survey of Canada Station 05CC001 (Blindman River near Blackfalds)
+when it is operational; or
+(b) at the point of diversion when the WSC station 05CC001 is not operational;
+(c) when diverting any water.
+3.20 The Licensee shall not divert water when the water temperature in the source of water
+exceeds 22oC.
+MONITORING AND REPORTING
+4.0 Unless otherwise authorized in writing by the Director, the Licensee shall:
+(a) measure the total volume of water diverted each month, from the source of
+water, using the meter specified in 3.10(a);
+(b) measure the rate of diversion on a continuous basis, from the source of water,
+using the meter specified in 3.10(b);
+(c) measure or provide a Volume Estimate of the total volume of water used for each
+Associated Operation and the water use per well licenced under the Oil and Gas
+Conservation Act;
+(d) record the surface legal land location(s) where diverted water is being used, and
+the purpose/operation for which it is being used;
+(e) when applicable, measure the total volume of water released to the environment;
+(f) for the calendar year, compare the water diversion and usage as per 4.0 (a) to
+the estimates submitted with the Application and any previous reporting;
+(g) for the upcoming calendar year, prepare an overall estimate of the monthly water
+diversion and usage that i</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1001,6 +1053,316 @@
         </is>
       </c>
       <c r="S10" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>temperature_window</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>monitoring_period</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>June</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>October</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Blindman</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence No.00458425-00-00
+File No.00458425
+Page 7 of 13
+(a) at the WSC Station No. 05CC001;
+(b) daily during diversion;
+or as otherwise authorized in writing by the Director.
+4.2 When the Water Survey of Canada Station No.05CC001 (Blindman River near
+Blackfalds) is not operational, the Licensee shall measure the rate of flow of water in the
+source:
+(a) at the point of diversion;
+(i) a minimum of weekly when the measured rate of flow is less than or equal to
+0.5 cubic metres per second;
+(ii) a minimum of bi-weekly when the measured rate of flow is greater than 0.5
+cubic meters per second.
+during diversion, or as otherwise authorized in writing by the Director.
+4.3 The Licensee shall monitor the rate of flow in the Red Deer River a minimum of bi-
+weekly during diversion.
+4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the
+source of water the point of diversion, at a minimum of the following:
+(a) prior to commencing diversion of water to establish a baseline temperature; and
+(b) if the baseline temperature:
+(i) is greater than 19oC, measure the temperature hourly during diversion; or
+(ii) any previous temperature measurement is less than 19oC, measure the
+temperature daily during diversion.
+4.5 The Licensee shall record and retain all of the following information for a minimum of 5
+years after being collected:
+(a) the place, date and time of all monitoring and measuring;
+(b) the results obtained pursuant to 4.0, 4.1, 4.2, 4.3 and 6.1; and
+(c) the </t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>temperature_rule</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>baseline_temperature_trigger</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Blindman</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence No.00458425-00-00
+File No.00458425
+Page 7 of 13
+(a) at the WSC Station No. 05CC001;
+(b) daily during diversion;
+or as otherwise authorized in writing by the Director.
+4.2 When the Water Survey of Canada Station No.05CC001 (Blindman River near
+Blackfalds) is not operational, the Licensee shall measure the rate of flow of water in the
+source:
+(a) at the point of diversion;
+(i) a minimum of weekly when the measured rate of flow is less than or equal to
+0.5 cubic metres per second;
+(ii) a minimum of bi-weekly when the measured rate of flow is greater than 0.5
+cubic meters per second.
+during diversion, or as otherwise authorized in writing by the Director.
+4.3 The Licensee shall monitor the rate of flow in the Red Deer River a minimum of bi-
+weekly during diversion.
+4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the
+source of water the point of diversion, at a minimum of the following:
+(a) prior to commencing diversion of water to establish a baseline temperature; and
+(b) if the baseline temperature:
+(i) is greater than 19oC, measure the temperature hourly during diversion; or
+(ii) any previous temperature measurement is less than 19oC, measure the
+temperature daily during diversion.
+4.5 The Licensee shall record and retain all of the following information for a minimum of 5
+years after being collected:
+(a) the place, date and time of all monitoring and measuring;
+(b) the results obtained pursuant to 4.0, 4.1, 4.2, 4.3 and 6.1; and
+(c) the </t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>temperature_rule</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>temperature_monitoring_frequency</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Blindman</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>hourly</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence No.00458425-00-00
+File No.00458425
+Page 7 of 13
+(a) at the WSC Station No. 05CC001;
+(b) daily during diversion;
+or as otherwise authorized in writing by the Director.
+4.2 When the Water Survey of Canada Station No.05CC001 (Blindman River near
+Blackfalds) is not operational, the Licensee shall measure the rate of flow of water in the
+source:
+(a) at the point of diversion;
+(i) a minimum of weekly when the measured rate of flow is less than or equal to
+0.5 cubic metres per second;
+(ii) a minimum of bi-weekly when the measured rate of flow is greater than 0.5
+cubic meters per second.
+during diversion, or as otherwise authorized in writing by the Director.
+4.3 The Licensee shall monitor the rate of flow in the Red Deer River a minimum of bi-
+weekly during diversion.
+4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the
+source of water the point of diversion, at a minimum of the following:
+(a) prior to commencing diversion of water to establish a baseline temperature; and
+(b) if the baseline temperature:
+(i) is greater than 19oC, measure the temperature hourly during diversion; or
+(ii) any previous temperature measurement is less than 19oC, measure the
+temperature daily during diversion.
+4.5 The Licensee shall record and retain all of the following information for a minimum of 5
+years after being collected:
+(a) the place, date and time of all monitoring and measuring;
+(b) the results obtained pursuant to 4.0, 4.1, 4.2, 4.3 and 6.1; and
+(c) the </t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="S13" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>temperature_rule</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>temperature_monitoring_frequency</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Blindman</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Licence No.00458425-00-00
+File No.00458425
+Page 7 of 13
+(a) at the WSC Station No. 05CC001;
+(b) daily during diversion;
+or as otherwise authorized in writing by the Director.
+4.2 When the Water Survey of Canada Station No.05CC001 (Blindman River near
+Blackfalds) is not operational, the Licensee shall measure the rate of flow of water in the
+source:
+(a) at the point of diversion;
+(i) a minimum of weekly when the measured rate of flow is less than or equal to
+0.5 cubic metres per second;
+(ii) a minimum of bi-weekly when the measured rate of flow is greater than 0.5
+cubic meters per second.
+during diversion, or as otherwise authorized in writing by the Director.
+4.3 The Licensee shall monitor the rate of flow in the Red Deer River a minimum of bi-
+weekly during diversion.
+4.4 Between June 1 and October 1, the Licensee shall measure the temperature of the
+source of water the point of diversion, at a minimum of the following:
+(a) prior to commencing diversion of water to establish a baseline temperature; and
+(b) if the baseline temperature:
+(i) is greater than 19oC, measure the temperature hourly during diversion; or
+(ii) any previous temperature measurement is less than 19oC, measure the
+temperature daily during diversion.
+4.5 The Licensee shall record and retain all of the following information for a minimum of 5
+years after being collected:
+(a) the place, date and time of all monitoring and measuring;
+(b) the results obtained pursuant to 4.0, 4.1, 4.2, 4.3 and 6.1; and
+(c) the </t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>00458425-00-00.pdf</t>
+        </is>
+      </c>
+      <c r="S14" t="n">
         <v>8</v>
       </c>
     </row>

--- a/data/outputs/extracted_rules.xlsx
+++ b/data/outputs/extracted_rules.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,30 +484,35 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>frequency_condition</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>units</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>station_id</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>station_name</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>source_text</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>source_pdf</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>page_no</t>
         </is>
@@ -537,32 +542,33 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less than the Instream Objective of 0.16 cubic meters per second;</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -590,32 +596,33 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less than the Instream Objective of 0.16 cubic meters per second;</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -643,32 +650,33 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>05CC002</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Red Deer River at Red Deer</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red Deer River that is 45% of the natural rate of flow or 16 cubic meters per second, whichever is greater at any point in time.</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -696,32 +704,33 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>05CB007</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Dickson Dam Tunnel Outlet</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red Deer River that is 45% of the natural rate of flow or 16 cubic meters per second, whichever is greater at any point in time.</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -750,27 +759,28 @@
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters per second;</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>6</v>
       </c>
     </row>
@@ -799,27 +809,28 @@
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5 cubic meters per second; when the flow in the Blindman River is greater than 0.5 cubic meters per second.</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -854,17 +865,18 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>05CC002</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Red Deer River at Red Deer</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -893,12 +905,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>6</v>
       </c>
     </row>
@@ -933,17 +945,18 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>05CB007</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Dickson Dam Tunnel Outlet</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -972,12 +985,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1009,14 +1022,15 @@
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -1047,12 +1061,12 @@
 diversion and usage that i</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1097,7 +1111,8 @@
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t xml:space="preserve">Licence No.00458425-00-00
 File No.00458425
@@ -1130,12 +1145,12 @@
 (c) the </t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1167,14 +1182,15 @@
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t xml:space="preserve">Licence No.00458425-00-00
 File No.00458425
@@ -1207,12 +1223,12 @@
 (c) the </t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1246,10 +1262,15 @@
           <t>hourly</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>baseline temperature &gt; 19 C</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
         <is>
           <t xml:space="preserve">Licence No.00458425-00-00
 File No.00458425
@@ -1282,12 +1303,12 @@
 (c) the </t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1321,10 +1342,15 @@
           <t>daily</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>previous temperature measurement &lt; 19 C</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t xml:space="preserve">Licence No.00458425-00-00
 File No.00458425
@@ -1357,12 +1383,12 @@
 (c) the </t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>8</v>
       </c>
     </row>

--- a/data/outputs/extracted_rules.xlsx
+++ b/data/outputs/extracted_rules.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T14"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,50 +469,65 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>flow_min_exclusive</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>flow_max_inclusive</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>max_diversion_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>temperature_c</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>frequency_condition</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>units</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>station_id</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>station_name</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>source_text</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>source_pdf</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>page_no</t>
         </is>
@@ -543,32 +558,35 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less than the Instream Objective of 0.16 cubic meters per second;</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="T2" t="n">
+      <c r="W2" t="n">
         <v>6</v>
       </c>
     </row>
@@ -597,32 +615,35 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>(a) 0 cubic meters per second, when the flow in the Blindman River is equal to or less than the Instream Objective of 0.16 cubic meters per second;</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="T3" t="n">
+      <c r="W3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -651,32 +672,35 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>05CC002</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Red Deer River at Red Deer</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red Deer River that is 45% of the natural rate of flow or 16 cubic meters per second, whichever is greater at any point in time.</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="T4" t="n">
+      <c r="W4" t="n">
         <v>6</v>
       </c>
     </row>
@@ -705,32 +729,35 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>m3/s</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>05CB007</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Dickson Dam Tunnel Outlet</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>3.16 The Water Conservation Objective for the Red Deer River is a rate of flow in the Red Deer River that is 45% of the natural rate of flow or 16 cubic meters per second, whichever is greater at any point in time.</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="T5" t="n">
+      <c r="W5" t="n">
         <v>6</v>
       </c>
     </row>
@@ -753,34 +780,45 @@
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>0.16</v>
+      </c>
       <c r="L6" t="n">
-        <v>10</v>
+        <v>0.5</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
+      <c r="O6" t="n">
+        <v>10</v>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>(b) 10% of the rate of flow in the Blindman River when the flow in the Blindman River is greater than 0.16 cubic meters per second but less than or equal to 0.5 cubic meters per second;</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>6</v>
       </c>
     </row>
@@ -803,34 +841,45 @@
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="n">
+      <c r="K7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
         <v>15</v>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>m3/s</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>05CC001</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Blindman River near Blackfalds</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>(c) 15% of the rate of flow in the Blindman River up to a maximum diversion rate of 0.5 cubic meters per second; when the flow in the Blindman River is greater than 0.5 cubic meters per second.</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -866,17 +915,20 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
         <is>
           <t>05CC002</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Red Deer River at Red Deer</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -905,12 +957,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>6</v>
       </c>
     </row>
@@ -946,17 +998,20 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
         <is>
           <t>05CB007</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Dickson Dam Tunnel Outlet</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -985,12 +1040,12 @@
 Deer River that is 45% of the natural rate of flow or 16 cubic meters per s</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="T9" t="n">
+      <c r="W9" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1017,20 +1072,23 @@
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="n">
-        <v>22</v>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="N10" t="n">
+        <v>22</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
         <is>
           <t>Licence No.00458425-00-00
 File No.00458425
@@ -1061,12 +1119,12 @@
 diversion and usage that i</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="T10" t="n">
+      <c r="W10" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1112,7 +1170,10 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
         <is>
           <t xml:space="preserve">Licence No.00458425-00-00
 File No.00458425
@@ -1145,12 +1206,12 @@
 (c) the </t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="T11" t="n">
+      <c r="W11" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1177,20 +1238,23 @@
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="n">
-        <v>19</v>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
+      <c r="N12" t="n">
+        <v>19</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
         <is>
           <t xml:space="preserve">Licence No.00458425-00-00
 File No.00458425
@@ -1223,12 +1287,12 @@
 (c) the </t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="T12" t="n">
+      <c r="W12" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1257,20 +1321,23 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
         <is>
           <t>hourly</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>baseline temperature &gt; 19 C</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
         <is>
           <t xml:space="preserve">Licence No.00458425-00-00
 File No.00458425
@@ -1303,12 +1370,12 @@
 (c) the </t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="T13" t="n">
+      <c r="W13" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1337,20 +1404,23 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>previous temperature measurement &lt; 19 C</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
         <is>
           <t xml:space="preserve">Licence No.00458425-00-00
 File No.00458425
@@ -1383,12 +1453,12 @@
 (c) the </t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>00458425-00-00.pdf</t>
         </is>
       </c>
-      <c r="T14" t="n">
+      <c r="W14" t="n">
         <v>8</v>
       </c>
     </row>
